--- a/Documents/Product Catalog/Office/Executive Table  Specifications.xlsx
+++ b/Documents/Product Catalog/Office/Executive Table  Specifications.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Talukder Furniture\Documents\Product Catalog\Office\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FC175B-6332-40D9-8599-D7199F0A34E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Table " sheetId="3" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Executive Table '!$B$1:$R$32</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -26,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="123">
   <si>
     <t>Antique</t>
   </si>
@@ -735,11 +738,14 @@
   <si>
     <t xml:space="preserve">Table </t>
   </si>
+  <si>
+    <t>Sub-Sub</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11">
     <font>
       <sz val="10"/>
@@ -1044,10 +1050,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1072,9 +1081,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1114,7 +1120,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1164,7 +1170,7 @@
         <xdr:cNvPr id="3" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000056010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000056010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1214,7 +1220,7 @@
         <xdr:cNvPr id="4" name="image2.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000057010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000057010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1264,7 +1270,7 @@
         <xdr:cNvPr id="5" name="image3.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000058010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000058010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1314,7 +1320,7 @@
         <xdr:cNvPr id="6" name="image4.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000059010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000059010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1364,7 +1370,7 @@
         <xdr:cNvPr id="7" name="image5.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005A010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005A010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1414,7 +1420,7 @@
         <xdr:cNvPr id="8" name="image7.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005B010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005B010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1464,7 +1470,7 @@
         <xdr:cNvPr id="9" name="image8.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005C010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005C010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1514,7 +1520,7 @@
         <xdr:cNvPr id="10" name="image9.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005D010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005D010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1564,7 +1570,7 @@
         <xdr:cNvPr id="11" name="image10.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005E010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005E010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1614,7 +1620,7 @@
         <xdr:cNvPr id="12" name="image11.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005F010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005F010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1664,7 +1670,7 @@
         <xdr:cNvPr id="13" name="image12.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000060010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000060010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1714,7 +1720,7 @@
         <xdr:cNvPr id="14" name="image13.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000061010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000061010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1764,7 +1770,7 @@
         <xdr:cNvPr id="15" name="image14.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000062010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000062010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1814,7 +1820,7 @@
         <xdr:cNvPr id="16" name="image15.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000063010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000063010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1864,7 +1870,7 @@
         <xdr:cNvPr id="17" name="image16.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000064010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000064010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1914,7 +1920,7 @@
         <xdr:cNvPr id="18" name="image17.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000065010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000065010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1964,7 +1970,7 @@
         <xdr:cNvPr id="19" name="image18.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000066010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000066010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2014,7 +2020,7 @@
         <xdr:cNvPr id="20" name="image19.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000067010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000067010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2064,7 +2070,7 @@
         <xdr:cNvPr id="21" name="image20.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000068010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000068010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2114,7 +2120,7 @@
         <xdr:cNvPr id="22" name="image21.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000069010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000069010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2164,7 +2170,7 @@
         <xdr:cNvPr id="23" name="image22.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00006A010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00006A010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2214,7 +2220,7 @@
         <xdr:cNvPr id="24" name="image23.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00006B010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00006B010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2264,7 +2270,7 @@
         <xdr:cNvPr id="25" name="image24.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00006C010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00006C010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2314,7 +2320,7 @@
         <xdr:cNvPr id="26" name="image25.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00006D010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00006D010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2364,7 +2370,7 @@
         <xdr:cNvPr id="27" name="image26.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00006E010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00006E010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2414,7 +2420,7 @@
         <xdr:cNvPr id="28" name="image27.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00006F010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00006F010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2464,7 +2470,7 @@
         <xdr:cNvPr id="29" name="image28.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000070010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000070010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2514,7 +2520,7 @@
         <xdr:cNvPr id="35" name="image34.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000076010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000076010000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2550,9 +2556,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2590,9 +2596,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2627,7 +2633,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2662,7 +2668,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2835,7 +2841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AT32"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -2858,89 +2864,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="20"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17" t="s">
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="K3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="16" t="s">
+      <c r="M3" s="16"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="R3" s="16" t="s">
         <v>74</v>
       </c>
       <c r="S3" s="2"/>
@@ -2973,20 +2979,22 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="23"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="15"/>
+      <c r="H4" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="I4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="25"/>
+        <v>122</v>
+      </c>
+      <c r="J4" s="16"/>
+      <c r="K4" s="26"/>
       <c r="L4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2996,10 +3004,10 @@
       <c r="N4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -3139,7 +3147,7 @@
         <v>60</v>
       </c>
       <c r="L6" s="5">
-        <f t="shared" ref="L6:L32" si="0">M6*(1-0.22)</f>
+        <f t="shared" ref="L6:L22" si="0">M6*(1-0.22)</f>
         <v>16770</v>
       </c>
       <c r="M6" s="10">
@@ -5271,11 +5279,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
@@ -5286,6 +5289,11 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>

--- a/Documents/Product Catalog/Office/Executive Table  Specifications.xlsx
+++ b/Documents/Product Catalog/Office/Executive Table  Specifications.xlsx
@@ -1050,15 +1050,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1077,10 +1068,19 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2864,89 +2864,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="20"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="17"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="22"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="19"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16" t="s">
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="16"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="18" t="s">
+      <c r="M3" s="22"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="P3" s="16" t="s">
+      <c r="P3" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="Q3" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="R3" s="22" t="s">
         <v>74</v>
       </c>
       <c r="S3" s="2"/>
@@ -2979,11 +2979,11 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="24"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
       <c r="G4" s="15" t="s">
         <v>11</v>
       </c>
@@ -2993,8 +2993,8 @@
       <c r="I4" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="J4" s="16"/>
-      <c r="K4" s="26"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="24"/>
       <c r="L4" s="1" t="s">
         <v>3</v>
       </c>
@@ -3004,10 +3004,10 @@
       <c r="N4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>

--- a/Documents/Product Catalog/Office/Executive Table  Specifications.xlsx
+++ b/Documents/Product Catalog/Office/Executive Table  Specifications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Talukder Furniture\Documents\Product Catalog\Office\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Talukder Furniture\Documents\Product Catalog\Office\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FC175B-6332-40D9-8599-D7199F0A34E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DAC622-94FA-4764-8212-58B0C2634CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3148,10 +3148,10 @@
       </c>
       <c r="L6" s="5">
         <f t="shared" ref="L6:L22" si="0">M6*(1-0.22)</f>
-        <v>16770</v>
+        <v>21060</v>
       </c>
       <c r="M6" s="10">
-        <v>21500</v>
+        <v>27000</v>
       </c>
       <c r="N6" s="12">
         <v>0.1</v>
@@ -3228,10 +3228,10 @@
       </c>
       <c r="L7" s="5">
         <f t="shared" si="0"/>
-        <v>16380</v>
+        <v>19500</v>
       </c>
       <c r="M7" s="10">
-        <v>21000</v>
+        <v>25000</v>
       </c>
       <c r="N7" s="12">
         <v>0.1</v>
@@ -3868,10 +3868,10 @@
       </c>
       <c r="L15" s="5">
         <f t="shared" si="0"/>
-        <v>8736</v>
+        <v>9516</v>
       </c>
       <c r="M15" s="10">
-        <v>11200</v>
+        <v>12200</v>
       </c>
       <c r="N15" s="12">
         <v>0.1</v>
@@ -4668,10 +4668,10 @@
       </c>
       <c r="L25" s="5">
         <f t="shared" si="1"/>
-        <v>9810</v>
+        <v>9630</v>
       </c>
       <c r="M25" s="10">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="N25" s="12">
         <v>0.1</v>
@@ -4908,10 +4908,10 @@
       </c>
       <c r="L28" s="5">
         <f t="shared" si="1"/>
-        <v>6930</v>
+        <v>5940</v>
       </c>
       <c r="M28" s="10">
-        <v>7700</v>
+        <v>6600</v>
       </c>
       <c r="N28" s="12">
         <v>0.1</v>
@@ -4988,10 +4988,10 @@
       </c>
       <c r="L29" s="5">
         <f t="shared" si="1"/>
-        <v>11790</v>
+        <v>13050</v>
       </c>
       <c r="M29" s="10">
-        <v>13100</v>
+        <v>14500</v>
       </c>
       <c r="N29" s="12">
         <v>0.1</v>
@@ -5068,10 +5068,10 @@
       </c>
       <c r="L30" s="5">
         <f t="shared" si="1"/>
-        <v>4860</v>
+        <v>5400</v>
       </c>
       <c r="M30" s="10">
-        <v>5400</v>
+        <v>6000</v>
       </c>
       <c r="N30" s="12">
         <v>0.1</v>
